--- a/output/pdf_financials_xlsx/XIGM.xlsx
+++ b/output/pdf_financials_xlsx/XIGM.xlsx
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.866083</v>
+        <v>4.036985</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>4.036985</v>
@@ -3503,7 +3503,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>1.170902</v>
       </c>

--- a/output/pdf_financials_xlsx/XIGM.xlsx
+++ b/output/pdf_financials_xlsx/XIGM.xlsx
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003891</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.034446</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.036852</v>
       </c>
     </row>
     <row r="35">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003891</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.034446</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.036852</v>
       </c>
     </row>
     <row r="37">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.090839</v>
+        <v>0.086948</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.07928399999999999</v>
+        <v>0.044838</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.066175</v>
+        <v>0.029323</v>
       </c>
     </row>
     <row r="49">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
